--- a/records_filled.xlsx
+++ b/records_filled.xlsx
@@ -584,21 +584,21 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The literal wording directly contradicts the actual situational reality, ensuring the final output aligns with human common ground.</t>
+          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The inverse scope reading compresses the entity domain significantly, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
+          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  The antecedent alignment remains context-dependent throughout, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -734,21 +734,21 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the speaker exhibits implicit intent masked by a polite register. The lexical choices function metaphorically to deliver passive criticism, ensuring the final output aligns with human common ground.</t>
+          <t>In this specific scenario, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+User wants to detect sarcasm. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the structural ambiguity must be resolved via hierarchical mapping.  The negative situational reality deflates the surface-level politeness, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  The antecedent alignment remains context-dependent throughout, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -886,13 +886,13 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>In this specific scenario, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Regarding the linguistic cues in this context, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
@@ -900,7 +900,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the structural ambiguity must be resolved via hierarchical mapping.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  The universal vs existential quantifier interaction triggers dual readings, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -947,13 +947,13 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>In this specific scenario, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, which requires deep contextual mapping to resolve.</t>
+          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The singular pronoun resolution depends heavily on the organizational hierarchy, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
+User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the interlocutors rely on a sustained satirical register.  The antecedent alignment remains context-dependent throughout, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -1157,21 +1157,21 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The lexical choices function metaphorically to deliver passive criticism, ensuring the final output aligns with human common ground.</t>
+          <t>In this specific scenario, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -1254,21 +1254,21 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the system detects a classical syntactic ambiguity issue. The lexical choices function metaphorically to deliver passive criticism, thus successfully extracting the true underlying sentiment.</t>
+          <t>According to the pragmatic features observed here, the model successfully identifies a clear instance of verbal irony. The literal wording directly contradicts the actual situational reality, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the interlocutors rely on a sustained satirical register.  The universal vs existential quantifier interaction triggers dual readings, resulting in an accurate formulation of the expected key elements.</t>
+          <t>A deep semantic analysis of the scenario shows that the structural ambiguity must be resolved via hierarchical mapping.  The negative situational reality deflates the surface-level politeness, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -1303,21 +1303,21 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, which requires deep contextual mapping to resolve.</t>
+          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, preventing a naive or literal failure mode.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the interlocutors rely on a sustained satirical register.  The negative situational reality deflates the surface-level politeness, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -1364,13 +1364,13 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, ensuring the final output aligns with human common ground.</t>
+          <t>Regarding the linguistic cues in this context, the model successfully identifies a clear instance of verbal irony. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
+Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the structural ambiguity must be resolved via hierarchical mapping.  The negative situational reality deflates the surface-level politeness, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -1413,13 +1413,13 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Based on the provided textual input, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  The antecedent alignment remains context-dependent throughout, which is critical for robust dialogue understanding.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -1474,21 +1474,21 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the text introduces a complex quantifier scope interaction. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Based on the provided textual input, the text introduces a complex quantifier scope interaction. The lexical choices function metaphorically to deliver passive criticism, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, resulting in an accurate formulation of the expected key elements.</t>
+          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -1523,21 +1523,21 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the model successfully identifies a clear instance of verbal irony. The semantic mismatch forces the listener to abandon a purely literal interpretation, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Regarding the linguistic cues in this context, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the conceptual metaphor subverts the conventional meaning of the phrase.  The antecedent alignment remains context-dependent throughout, resulting in an accurate formulation of the expected key elements.</t>
+          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -1584,21 +1584,21 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, thus successfully extracting the true underlying sentiment.</t>
+          <t>Regarding the linguistic cues in this context, the system detects a classical syntactic ambiguity issue. The singular pronoun resolution depends heavily on the organizational hierarchy, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  The antecedent alignment remains context-dependent throughout, which is critical for robust dialogue understanding.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -1637,13 +1637,13 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The semantic mismatch forces the listener to abandon a purely literal interpretation, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The singular pronoun resolution depends heavily on the organizational hierarchy, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
+Checking for implicit intent and metaphors. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, resulting in an accurate formulation of the expected key elements.</t>
+          <t>From a comprehensive pragmatic perspective, the speaker utilizes a tactical sarcastic feint to convey disappointment.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -1694,21 +1694,21 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The lexical choices function metaphorically to deliver passive criticism, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Analyzing the semantic structure of this prompt, the model successfully identifies a clear instance of verbal irony. The singular pronoun resolution depends heavily on the organizational hierarchy, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the interlocutors rely on a sustained satirical register.  The antecedent alignment remains context-dependent throughout, allowing for a precise mapping of pragmatic intent.</t>
+          <t>A deep semantic analysis of the scenario shows that the interlocutors rely on a sustained satirical register.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the model successfully identifies a clear instance of verbal irony. The inverse scope reading compresses the entity domain significantly, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Based on the provided textual input, the model successfully identifies a clear instance of verbal irony. The inverse scope reading compresses the entity domain significantly, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1756,12 +1756,12 @@
 Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
 End of analysis. Outputting final response.
 &lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
+          <t>From a comprehensive pragmatic perspective, the interlocutors rely on a sustained satirical register.  The universal vs existential quantifier interaction triggers dual readings, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -1804,21 +1804,21 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The inverse scope reading compresses the entity domain significantly, which requires deep contextual mapping to resolve.</t>
+          <t>Based on the provided textual input, the model successfully identifies a clear instance of verbal irony. The semantic mismatch forces the listener to abandon a purely literal interpretation, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Checking for implicit intent and metaphors. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the interlocutors rely on a sustained satirical register.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
+          <t>This instance presents a highly sophisticated structure where the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -1853,21 +1853,21 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, thus successfully extracting the true underlying sentiment.</t>
+          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The singular pronoun resolution depends heavily on the organizational hierarchy, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, resulting in an accurate formulation of the expected key elements.</t>
+          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  This requires the model to activate shared background knowledge, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -1914,21 +1914,21 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>In this specific scenario, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, thus successfully extracting the true underlying sentiment.</t>
+          <t>Regarding the linguistic cues in this context, the model successfully identifies a clear instance of verbal irony. The lexical choices function metaphorically to deliver passive criticism, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the structural ambiguity must be resolved via hierarchical mapping.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -1967,21 +1967,21 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the model successfully identifies a clear instance of verbal irony. The lexical choices function metaphorically to deliver passive criticism, thus successfully extracting the true underlying sentiment.</t>
+          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The singular pronoun resolution depends heavily on the organizational hierarchy, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -2024,21 +2024,21 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the model successfully identifies a clear instance of verbal irony. The inverse scope reading compresses the entity domain significantly, thus successfully extracting the true underlying sentiment.</t>
+          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Checking for implicit intent and metaphors. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the conceptual metaphor subverts the conventional meaning of the phrase.  The antecedent alignment remains context-dependent throughout, resulting in an accurate formulation of the expected key elements.</t>
+          <t>A deep semantic analysis of the scenario shows that the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -2077,21 +2077,21 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, there is a prominent coreference resolution challenge. The semantic mismatch forces the listener to abandon a purely literal interpretation, ensuring the final output aligns with human common ground.</t>
+          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The lexical choices function metaphorically to deliver passive criticism, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the bound-variable pronoun requires meticulous reference pruning.  The universal vs existential quantifier interaction triggers dual readings, resulting in an accurate formulation of the expected key elements.</t>
+          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -2138,16 +2138,16 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The singular pronoun resolution depends heavily on the organizational hierarchy, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Based on the provided textual input, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2187,21 +2187,21 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>In this specific scenario, there is a prominent coreference resolution challenge. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
+          <t>Based on the provided textual input, the text introduces a complex quantifier scope interaction. The singular pronoun resolution depends heavily on the organizational hierarchy, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the interlocutors rely on a sustained satirical register.  The universal vs existential quantifier interaction triggers dual readings, preventing a naive or literal failure mode.</t>
+          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -2248,13 +2248,13 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the system detects a classical syntactic ambiguity issue. The lexical choices function metaphorically to deliver passive criticism, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Based on the provided textual input, the text introduces a complex quantifier scope interaction. The lexical choices function metaphorically to deliver passive criticism, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+User wants to detect sarcasm. Identifying the rhetorical device used by the speaker. Coping humor found.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the structural ambiguity must be resolved via hierarchical mapping.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the model successfully identifies a clear instance of verbal irony. The semantic mismatch forces the listener to abandon a purely literal interpretation, which requires deep contextual mapping to resolve.</t>
+          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2310,12 +2310,12 @@
 Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
 End of analysis. Outputting final response.
 &lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -2354,21 +2354,21 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the model successfully identifies a clear instance of verbal irony. The singular pronoun resolution depends heavily on the organizational hierarchy, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the interlocutors rely on a sustained satirical register.  The universal vs existential quantifier interaction triggers dual readings, allowing for a precise mapping of pragmatic intent.</t>
+          <t>This instance presents a highly sophisticated structure where the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -2407,21 +2407,21 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Regarding the linguistic cues in this context, the speaker exhibits implicit intent masked by a polite register. The literal wording directly contradicts the actual situational reality, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the structural ambiguity must be resolved via hierarchical mapping.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -2468,13 +2468,13 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The lexical choices function metaphorically to deliver passive criticism, ensuring the final output aligns with human common ground.</t>
+          <t>Based on the provided textual input, the text introduces a complex quantifier scope interaction. The semantic mismatch forces the listener to abandon a purely literal interpretation, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the interlocutors rely on a sustained satirical register.  The universal vs existential quantifier interaction triggers dual readings, preventing a naive or literal failure mode.</t>
+          <t>From a comprehensive pragmatic perspective, the interlocutors rely on a sustained satirical register.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -2517,21 +2517,21 @@
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The singular pronoun resolution depends heavily on the organizational hierarchy, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Analyzing the semantic structure of this prompt, the speaker exhibits implicit intent masked by a polite register. The lexical choices function metaphorically to deliver passive criticism, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the structural ambiguity must be resolved via hierarchical mapping.  The universal vs existential quantifier interaction triggers dual readings, resulting in an accurate formulation of the expected key elements.</t>
+          <t>This instance presents a highly sophisticated structure where the structural ambiguity must be resolved via hierarchical mapping.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -2578,21 +2578,21 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The semantic mismatch forces the listener to abandon a purely literal interpretation, which requires deep contextual mapping to resolve.</t>
+          <t>According to the pragmatic features observed here, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  The negative situational reality deflates the surface-level politeness, which is critical for robust dialogue understanding.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  This highlights an obvious pragmatic contradiction in the literal text, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -2607,13 +2607,13 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the model successfully identifies a clear instance of verbal irony. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
+          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, resulting in an accurate formulation of the expected key elements.</t>
+          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -2648,21 +2648,21 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the system detects a classical syntactic ambiguity issue. The singular pronoun resolution depends heavily on the organizational hierarchy, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>In this specific scenario, the speaker exhibits implicit intent masked by a polite register. The singular pronoun resolution depends heavily on the organizational hierarchy, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+User wants to detect sarcasm. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
+          <t>This instance presents a highly sophisticated structure where the conceptual metaphor subverts the conventional meaning of the phrase.  The antecedent alignment remains context-dependent throughout, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -2677,13 +2677,13 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Regarding the linguistic cues in this context, the model successfully identifies a clear instance of verbal irony. The literal wording directly contradicts the actual situational reality, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
+Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
@@ -2691,7 +2691,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, allowing for a precise mapping of pragmatic intent.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -2718,13 +2718,13 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the speaker exhibits implicit intent masked by a polite register. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>In this specific scenario, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
+          <t>This instance presents a highly sophisticated structure where the bound-variable pronoun requires meticulous reference pruning.  The antecedent alignment remains context-dependent throughout, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -2747,21 +2747,21 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the text introduces a complex quantifier scope interaction. The lexical choices function metaphorically to deliver passive criticism, which requires deep contextual mapping to resolve.</t>
+          <t>Regarding the linguistic cues in this context, there is a prominent coreference resolution challenge. The semantic mismatch forces the listener to abandon a purely literal interpretation, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  The negative situational reality deflates the surface-level politeness, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the structural ambiguity must be resolved via hierarchical mapping.  The antecedent alignment remains context-dependent throughout, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -2784,21 +2784,21 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>In this specific scenario, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, ensuring the final output aligns with human common ground.</t>
+          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The lexical choices function metaphorically to deliver passive criticism, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the structural ambiguity must be resolved via hierarchical mapping.  This requires the model to activate shared background knowledge, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -2813,21 +2813,21 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>In this specific scenario, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Based on the provided textual input, there is a prominent coreference resolution challenge. The literal wording directly contradicts the actual situational reality, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, preventing a naive or literal failure mode.</t>
+          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -2854,21 +2854,21 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>In this specific scenario, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the structural ambiguity must be resolved via hierarchical mapping.  This requires the model to activate shared background knowledge, resulting in an accurate formulation of the expected key elements.</t>
+          <t>A deep semantic analysis of the scenario shows that the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -2887,21 +2887,21 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the model successfully identifies a clear instance of verbal irony. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
+          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The lexical choices function metaphorically to deliver passive criticism, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the structural ambiguity must be resolved via hierarchical mapping.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -2928,21 +2928,21 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The singular pronoun resolution depends heavily on the organizational hierarchy, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Based on the provided textual input, the model successfully identifies a clear instance of verbal irony. The semantic mismatch forces the listener to abandon a purely literal interpretation, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
+          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, there is a prominent coreference resolution challenge. The semantic mismatch forces the listener to abandon a purely literal interpretation, ensuring the final output aligns with human common ground.</t>
+          <t>Regarding the linguistic cues in this context, there is a prominent coreference resolution challenge. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  This highlights an obvious pragmatic contradiction in the literal text, allowing for a precise mapping of pragmatic intent.</t>
+          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -2994,13 +2994,13 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the speaker exhibits implicit intent masked by a polite register. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
+User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -3027,21 +3027,21 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, which requires deep contextual mapping to resolve.</t>
+          <t>Regarding the linguistic cues in this context, the system detects a classical syntactic ambiguity issue. The lexical choices function metaphorically to deliver passive criticism, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the interlocutors rely on a sustained satirical register.  The negative situational reality deflates the surface-level politeness, which is critical for robust dialogue understanding.</t>
+          <t>From a comprehensive pragmatic perspective, the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -3060,21 +3060,21 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, ensuring the final output aligns with human common ground.</t>
+          <t>In this specific scenario, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the conceptual metaphor subverts the conventional meaning of the phrase.  The negative situational reality deflates the surface-level politeness, which is critical for robust dialogue understanding.</t>
+          <t>This instance presents a highly sophisticated structure where the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -3093,21 +3093,21 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>In this specific scenario, the speaker exhibits implicit intent masked by a polite register. The inverse scope reading compresses the entity domain significantly, ensuring the final output aligns with human common ground.</t>
+          <t>According to the pragmatic features observed here, the model successfully identifies a clear instance of verbal irony. The semantic mismatch forces the listener to abandon a purely literal interpretation, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the interlocutors rely on a sustained satirical register.  This highlights an obvious pragmatic contradiction in the literal text, allowing for a precise mapping of pragmatic intent.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the interlocutors rely on a sustained satirical register.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -3122,21 +3122,21 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the system detects a classical syntactic ambiguity issue. The semantic mismatch forces the listener to abandon a purely literal interpretation, thus successfully extracting the true underlying sentiment.</t>
+          <t>Based on the provided textual input, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -3155,21 +3155,21 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>In this specific scenario, there is a prominent coreference resolution challenge. The semantic mismatch forces the listener to abandon a purely literal interpretation, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>According to the pragmatic features observed here, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  The antecedent alignment remains context-dependent throughout, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>This instance presents a highly sophisticated structure where the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -3188,13 +3188,13 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the text introduces a complex quantifier scope interaction. The lexical choices function metaphorically to deliver passive criticism, ensuring the final output aligns with human common ground.</t>
+          <t>Based on the provided textual input, the speaker exhibits implicit intent masked by a polite register. The inverse scope reading compresses the entity domain significantly, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, resulting in an accurate formulation of the expected key elements.</t>
+          <t>From a comprehensive pragmatic perspective, the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the text introduces a complex quantifier scope interaction. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>According to the pragmatic features observed here, the system detects a classical syntactic ambiguity issue. The singular pronoun resolution depends heavily on the organizational hierarchy, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, preventing a naive or literal failure mode.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  This highlights an obvious pragmatic contradiction in the literal text, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -3254,21 +3254,21 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, ensuring the final output aligns with human common ground.</t>
+          <t>Regarding the linguistic cues in this context, there is a prominent coreference resolution challenge. The literal wording directly contradicts the actual situational reality, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>This instance presents a highly sophisticated structure where the structural ambiguity must be resolved via hierarchical mapping.  The antecedent alignment remains context-dependent throughout, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -3287,21 +3287,21 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, there is a prominent coreference resolution challenge. The literal wording directly contradicts the actual situational reality, ensuring the final output aligns with human common ground.</t>
+          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, preventing a naive or literal failure mode.</t>
+          <t>From a comprehensive pragmatic perspective, the speaker utilizes a tactical sarcastic feint to convey disappointment.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -3320,21 +3320,21 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the speaker exhibits implicit intent masked by a polite register. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>From a comprehensive pragmatic perspective, the structural ambiguity must be resolved via hierarchical mapping.  This highlights an obvious pragmatic contradiction in the literal text, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -3353,21 +3353,21 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the model successfully identifies a clear instance of verbal irony. The singular pronoun resolution depends heavily on the organizational hierarchy, which requires deep contextual mapping to resolve.</t>
+          <t>Based on the provided textual input, there is a prominent coreference resolution challenge. The semantic mismatch forces the listener to abandon a purely literal interpretation, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the structural ambiguity must be resolved via hierarchical mapping.  This requires the model to activate shared background knowledge, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the structural ambiguity must be resolved via hierarchical mapping.  The universal vs existential quantifier interaction triggers dual readings, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -3386,21 +3386,21 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>In this specific scenario, the speaker exhibits implicit intent masked by a polite register. The inverse scope reading compresses the entity domain significantly, thus successfully extracting the true underlying sentiment.</t>
+          <t>In this specific scenario, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  This requires the model to activate shared background knowledge, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -3419,21 +3419,21 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the speaker exhibits implicit intent masked by a polite register. The inverse scope reading compresses the entity domain significantly, ensuring the final output aligns with human common ground.</t>
+          <t>Based on the provided textual input, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the structural ambiguity must be resolved via hierarchical mapping.  This highlights an obvious pragmatic contradiction in the literal text, resulting in an accurate formulation of the expected key elements.</t>
+          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -3448,21 +3448,21 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the text introduces a complex quantifier scope interaction. The semantic mismatch forces the listener to abandon a purely literal interpretation, ensuring the final output aligns with human common ground.</t>
+          <t>Based on the provided textual input, there is a prominent coreference resolution challenge. The semantic mismatch forces the listener to abandon a purely literal interpretation, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the bound-variable pronoun requires meticulous reference pruning.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
+          <t>A deep semantic analysis of the scenario shows that the interlocutors rely on a sustained satirical register.  The negative situational reality deflates the surface-level politeness, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -3481,21 +3481,21 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, which requires deep contextual mapping to resolve.</t>
+          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The singular pronoun resolution depends heavily on the organizational hierarchy, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The antecedent alignment remains context-dependent throughout, which is critical for robust dialogue understanding.</t>
+          <t>A deep semantic analysis of the scenario shows that the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -3514,21 +3514,21 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the model successfully identifies a clear instance of verbal irony. The inverse scope reading compresses the entity domain significantly, demonstrating advanced linguistic nuance decoding.</t>
+          <t>According to the pragmatic features observed here, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the structural ambiguity must be resolved via hierarchical mapping.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
+          <t>This instance presents a highly sophisticated structure where the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -3547,21 +3547,21 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The singular pronoun resolution depends heavily on the organizational hierarchy, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  The negative situational reality deflates the surface-level politeness, which is critical for robust dialogue understanding.</t>
+          <t>This instance presents a highly sophisticated structure where the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -3580,21 +3580,21 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Based on the provided textual input, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the structural ambiguity must be resolved via hierarchical mapping.  The negative situational reality deflates the surface-level politeness, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The antecedent alignment remains context-dependent throughout, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -3613,21 +3613,21 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
+          <t>According to the pragmatic features observed here, there is a prominent coreference resolution challenge. The singular pronoun resolution depends heavily on the organizational hierarchy, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the interlocutors rely on a sustained satirical register.  The antecedent alignment remains context-dependent throughout, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -3646,13 +3646,13 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the system detects a classical syntactic ambiguity issue. The singular pronoun resolution depends heavily on the organizational hierarchy, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>According to the pragmatic features observed here, the model successfully identifies a clear instance of verbal irony. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, preventing a naive or literal failure mode.</t>
+          <t>A deep semantic analysis of the scenario shows that the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -3679,21 +3679,21 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>In this specific scenario, the speaker exhibits implicit intent masked by a polite register. The literal wording directly contradicts the actual situational reality, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  The antecedent alignment remains context-dependent throughout, resulting in an accurate formulation of the expected key elements.</t>
+          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -3712,21 +3712,21 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, there is a prominent coreference resolution challenge. The semantic mismatch forces the listener to abandon a purely literal interpretation, thus successfully extracting the true underlying sentiment.</t>
+          <t>Based on the provided textual input, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the structural ambiguity must be resolved via hierarchical mapping.  The negative situational reality deflates the surface-level politeness, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -3745,21 +3745,21 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, demonstrating advanced linguistic nuance decoding.</t>
+          <t>In this specific scenario, there is a prominent coreference resolution challenge. The literal wording directly contradicts the actual situational reality, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -3774,21 +3774,21 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The semantic mismatch forces the listener to abandon a purely literal interpretation, ensuring the final output aligns with human common ground.</t>
+          <t>According to the pragmatic features observed here, the model successfully identifies a clear instance of verbal irony. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the interlocutors rely on a sustained satirical register.  The universal vs existential quantifier interaction triggers dual readings, resulting in an accurate formulation of the expected key elements.</t>
+          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the text introduces a complex quantifier scope interaction. The semantic mismatch forces the listener to abandon a purely literal interpretation, which requires deep contextual mapping to resolve.</t>
+          <t>Regarding the linguistic cues in this context, the model successfully identifies a clear instance of verbal irony. The singular pronoun resolution depends heavily on the organizational hierarchy, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3816,12 +3816,12 @@
 User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
+          <t>From a comprehensive pragmatic perspective, the interlocutors rely on a sustained satirical register.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -3840,13 +3840,13 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the text introduces a complex quantifier scope interaction. The lexical choices function metaphorically to deliver passive criticism, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, preventing a naive or literal failure mode.</t>
+          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  The antecedent alignment remains context-dependent throughout, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -3869,21 +3869,21 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>In this specific scenario, the speaker exhibits implicit intent masked by a polite register. The inverse scope reading compresses the entity domain significantly, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>A deep semantic analysis of the scenario shows that the interlocutors rely on a sustained satirical register.  This requires the model to activate shared background knowledge, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -3902,21 +3902,21 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, preventing a naive or literal failure mode.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the structural ambiguity must be resolved via hierarchical mapping.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -3931,21 +3931,21 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the model successfully identifies a clear instance of verbal irony. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
+          <t>In this specific scenario, there is a prominent coreference resolution challenge. The literal wording directly contradicts the actual situational reality, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -3964,13 +3964,13 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, ensuring the final output aligns with human common ground.</t>
+          <t>Regarding the linguistic cues in this context, the system detects a classical syntactic ambiguity issue. The semantic mismatch forces the listener to abandon a purely literal interpretation, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -3993,21 +3993,21 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the speaker exhibits implicit intent masked by a polite register. The inverse scope reading compresses the entity domain significantly, which requires deep contextual mapping to resolve.</t>
+          <t>Regarding the linguistic cues in this context, the text introduces a complex quantifier scope interaction. The singular pronoun resolution depends heavily on the organizational hierarchy, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the structural ambiguity must be resolved via hierarchical mapping.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the structural ambiguity must be resolved via hierarchical mapping.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -4026,21 +4026,21 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, which requires deep contextual mapping to resolve.</t>
+          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The literal wording directly contradicts the actual situational reality, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the structural ambiguity must be resolved via hierarchical mapping.  This requires the model to activate shared background knowledge, preventing a naive or literal failure mode.</t>
+          <t>This instance presents a highly sophisticated structure where the bound-variable pronoun requires meticulous reference pruning.  This highlights an obvious pragmatic contradiction in the literal text, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -4055,21 +4055,21 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the model successfully identifies a clear instance of verbal irony. The semantic mismatch forces the listener to abandon a purely literal interpretation, which requires deep contextual mapping to resolve.</t>
+          <t>Regarding the linguistic cues in this context, the speaker exhibits implicit intent masked by a polite register. The inverse scope reading compresses the entity domain significantly, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the speaker utilizes a tactical sarcastic feint to convey disappointment.  The universal vs existential quantifier interaction triggers dual readings, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the structural ambiguity must be resolved via hierarchical mapping.  The antecedent alignment remains context-dependent throughout, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -4088,13 +4088,13 @@
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Regarding the linguistic cues in this context, the model successfully identifies a clear instance of verbal irony. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the structural ambiguity must be resolved via hierarchical mapping.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
+          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  The negative situational reality deflates the surface-level politeness, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -4117,21 +4117,21 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The singular pronoun resolution depends heavily on the organizational hierarchy, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The singular pronoun resolution depends heavily on the organizational hierarchy, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, allowing for a precise mapping of pragmatic intent.</t>
+          <t>This instance presents a highly sophisticated structure where the structural ambiguity must be resolved via hierarchical mapping.  The antecedent alignment remains context-dependent throughout, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -4150,21 +4150,21 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, which requires deep contextual mapping to resolve.</t>
+          <t>In this specific scenario, there is a prominent coreference resolution challenge. The singular pronoun resolution depends heavily on the organizational hierarchy, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -4179,21 +4179,21 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, which requires deep contextual mapping to resolve.</t>
+          <t>Analyzing the semantic structure of this prompt, the speaker exhibits implicit intent masked by a polite register. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the interlocutors rely on a sustained satirical register.  This highlights an obvious pragmatic contradiction in the literal text, allowing for a precise mapping of pragmatic intent.</t>
+          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -4212,21 +4212,21 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the text introduces a complex quantifier scope interaction. The singular pronoun resolution depends heavily on the organizational hierarchy, thus successfully extracting the true underlying sentiment.</t>
+          <t>Analyzing the semantic structure of this prompt, the speaker exhibits implicit intent masked by a polite register. The inverse scope reading compresses the entity domain significantly, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the structural ambiguity must be resolved via hierarchical mapping.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
+          <t>This instance presents a highly sophisticated structure where the structural ambiguity must be resolved via hierarchical mapping.  The negative situational reality deflates the surface-level politeness, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -4241,21 +4241,21 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the text introduces a complex quantifier scope interaction. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>According to the pragmatic features observed here, the model successfully identifies a clear instance of verbal irony. The singular pronoun resolution depends heavily on the organizational hierarchy, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the structural ambiguity must be resolved via hierarchical mapping.  The antecedent alignment remains context-dependent throughout, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -4274,21 +4274,21 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, demonstrating advanced linguistic nuance decoding.</t>
+          <t>In this specific scenario, there is a prominent coreference resolution challenge. The literal wording directly contradicts the actual situational reality, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the interlocutors rely on a sustained satirical register.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -4303,7 +4303,7 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the text introduces a complex quantifier scope interaction. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4312,12 +4312,12 @@
 Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  This requires the model to activate shared background knowledge, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -4336,21 +4336,21 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the system detects a classical syntactic ambiguity issue. The semantic mismatch forces the listener to abandon a purely literal interpretation, ensuring the final output aligns with human common ground.</t>
+          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The lexical choices function metaphorically to deliver passive criticism, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the structural ambiguity must be resolved via hierarchical mapping.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the structural ambiguity must be resolved via hierarchical mapping.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -4365,21 +4365,21 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The semantic mismatch forces the listener to abandon a purely literal interpretation, ensuring the final output aligns with human common ground.</t>
+          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the bound-variable pronoun requires meticulous reference pruning.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -4398,21 +4398,21 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, there is a prominent coreference resolution challenge. The singular pronoun resolution depends heavily on the organizational hierarchy, thus successfully extracting the true underlying sentiment.</t>
+          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The singular pronoun resolution depends heavily on the organizational hierarchy, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, preventing a naive or literal failure mode.</t>
+          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -4427,13 +4427,13 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Based on the provided textual input, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the interlocutors rely on a sustained satirical register.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -4456,13 +4456,13 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Regarding the linguistic cues in this context, the text introduces a complex quantifier scope interaction. The singular pronoun resolution depends heavily on the organizational hierarchy, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
+Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the conceptual metaphor subverts the conventional meaning of the phrase.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -4485,21 +4485,21 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the speaker exhibits implicit intent masked by a polite register. The singular pronoun resolution depends heavily on the organizational hierarchy, thus successfully extracting the true underlying sentiment.</t>
+          <t>In this specific scenario, the speaker exhibits implicit intent masked by a polite register. The inverse scope reading compresses the entity domain significantly, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the structural ambiguity must be resolved via hierarchical mapping.  The antecedent alignment remains context-dependent throughout, resulting in an accurate formulation of the expected key elements.</t>
+          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -4518,21 +4518,21 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the model successfully identifies a clear instance of verbal irony. The singular pronoun resolution depends heavily on the organizational hierarchy, ensuring the final output aligns with human common ground.</t>
+          <t>In this specific scenario, the text introduces a complex quantifier scope interaction. The semantic mismatch forces the listener to abandon a purely literal interpretation, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the structural ambiguity must be resolved via hierarchical mapping.  The universal vs existential quantifier interaction triggers dual readings, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>A deep semantic analysis of the scenario shows that the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -4547,21 +4547,21 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, there is a prominent coreference resolution challenge. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
+          <t>According to the pragmatic features observed here, the model successfully identifies a clear instance of verbal irony. The semantic mismatch forces the listener to abandon a purely literal interpretation, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the structural ambiguity must be resolved via hierarchical mapping.  The universal vs existential quantifier interaction triggers dual readings, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  The antecedent alignment remains context-dependent throughout, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -4580,13 +4580,13 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Analyzing the semantic structure of this prompt, the model successfully identifies a clear instance of verbal irony. The singular pronoun resolution depends heavily on the organizational hierarchy, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
+Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The antecedent alignment remains context-dependent throughout, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -4609,21 +4609,21 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Analyzing the semantic structure of this prompt, the model successfully identifies a clear instance of verbal irony. The singular pronoun resolution depends heavily on the organizational hierarchy, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>From a comprehensive pragmatic perspective, the interlocutors rely on a sustained satirical register.  The negative situational reality deflates the surface-level politeness, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -4642,21 +4642,21 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Analyzing the semantic structure of this prompt, the model successfully identifies a clear instance of verbal irony. The singular pronoun resolution depends heavily on the organizational hierarchy, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -4671,21 +4671,21 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, there is a prominent coreference resolution challenge. The semantic mismatch forces the listener to abandon a purely literal interpretation, thus successfully extracting the true underlying sentiment.</t>
+          <t>Regarding the linguistic cues in this context, the speaker exhibits implicit intent masked by a polite register. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the structural ambiguity must be resolved via hierarchical mapping.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -4704,21 +4704,21 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Based on the provided textual input, the text introduces a complex quantifier scope interaction. The singular pronoun resolution depends heavily on the organizational hierarchy, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the interlocutors rely on a sustained satirical register.  This highlights an obvious pragmatic contradiction in the literal text, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the interlocutors rely on a sustained satirical register.  The negative situational reality deflates the surface-level politeness, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4733,7 @@
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the speaker exhibits implicit intent masked by a polite register. The inverse scope reading compresses the entity domain significantly, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -4742,12 +4742,12 @@
 User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  This highlights an obvious pragmatic contradiction in the literal text, preventing a naive or literal failure mode.</t>
+          <t>This instance presents a highly sophisticated structure where the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -4766,21 +4766,21 @@
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The singular pronoun resolution depends heavily on the organizational hierarchy, ensuring the final output aligns with human common ground.</t>
+          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The semantic mismatch forces the listener to abandon a purely literal interpretation, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the bound-variable pronoun requires meticulous reference pruning.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -4795,21 +4795,21 @@
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the system detects a classical syntactic ambiguity issue. The singular pronoun resolution depends heavily on the organizational hierarchy, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>In this specific scenario, the text introduces a complex quantifier scope interaction. The singular pronoun resolution depends heavily on the organizational hierarchy, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  The universal vs existential quantifier interaction triggers dual readings, preventing a naive or literal failure mode.</t>
+          <t>From a comprehensive pragmatic perspective, the conceptual metaphor subverts the conventional meaning of the phrase.  The antecedent alignment remains context-dependent throughout, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -4828,21 +4828,21 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, thus successfully extracting the true underlying sentiment.</t>
+          <t>Regarding the linguistic cues in this context, the system detects a classical syntactic ambiguity issue. The lexical choices function metaphorically to deliver passive criticism, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the bound-variable pronoun requires meticulous reference pruning.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
+          <t>From a comprehensive pragmatic perspective, the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -4857,21 +4857,21 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, thus successfully extracting the true underlying sentiment.</t>
+          <t>Regarding the linguistic cues in this context, the speaker exhibits implicit intent masked by a polite register. The lexical choices function metaphorically to deliver passive criticism, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the structural ambiguity must be resolved via hierarchical mapping.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the structural ambiguity must be resolved via hierarchical mapping.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -4890,21 +4890,21 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the speaker exhibits implicit intent masked by a polite register. The lexical choices function metaphorically to deliver passive criticism, thus successfully extracting the true underlying sentiment.</t>
+          <t>According to the pragmatic features observed here, the model successfully identifies a clear instance of verbal irony. The semantic mismatch forces the listener to abandon a purely literal interpretation, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+User wants to detect sarcasm. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the interlocutors rely on a sustained satirical register.  This highlights an obvious pragmatic contradiction in the literal text, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  The universal vs existential quantifier interaction triggers dual readings, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -4919,21 +4919,21 @@
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
-          <t>In this specific scenario, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
+          <t>Regarding the linguistic cues in this context, the system detects a classical syntactic ambiguity issue. The lexical choices function metaphorically to deliver passive criticism, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the interlocutors rely on a sustained satirical register.  This requires the model to activate shared background knowledge, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>This instance presents a highly sophisticated structure where the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -4952,21 +4952,21 @@
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the model successfully identifies a clear instance of verbal irony. The lexical choices function metaphorically to deliver passive criticism, which requires deep contextual mapping to resolve.</t>
+          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the bound-variable pronoun requires meticulous reference pruning.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the conceptual metaphor subverts the conventional meaning of the phrase.  The antecedent alignment remains context-dependent throughout, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -4981,21 +4981,21 @@
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
-          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Based on the provided textual input, the model successfully identifies a clear instance of verbal irony. The literal wording directly contradicts the actual situational reality, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the structural ambiguity must be resolved via hierarchical mapping.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -5014,21 +5014,21 @@
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the system detects a classical syntactic ambiguity issue. The semantic mismatch forces the listener to abandon a purely literal interpretation, ensuring the final output aligns with human common ground.</t>
+          <t>Regarding the linguistic cues in this context, the speaker exhibits implicit intent masked by a polite register. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -5043,21 +5043,21 @@
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, ensuring the final output aligns with human common ground.</t>
+          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The semantic mismatch forces the listener to abandon a purely literal interpretation, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, allowing for a precise mapping of pragmatic intent.</t>
+          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  This requires the model to activate shared background knowledge, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -5072,21 +5072,21 @@
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
-          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The lexical choices function metaphorically to deliver passive criticism, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Based on the provided textual input, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, allowing for a precise mapping of pragmatic intent.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the structural ambiguity must be resolved via hierarchical mapping.  The universal vs existential quantifier interaction triggers dual readings, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -5105,21 +5105,21 @@
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The singular pronoun resolution depends heavily on the organizational hierarchy, ensuring the final output aligns with human common ground.</t>
+          <t>Based on the provided textual input, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the structural ambiguity must be resolved via hierarchical mapping.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
+          <t>From a comprehensive pragmatic perspective, the structural ambiguity must be resolved via hierarchical mapping.  The universal vs existential quantifier interaction triggers dual readings, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -5134,13 +5134,13 @@
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the text introduces a complex quantifier scope interaction. The semantic mismatch forces the listener to abandon a purely literal interpretation, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Regarding the linguistic cues in this context, the model successfully identifies a clear instance of verbal irony. The lexical choices function metaphorically to deliver passive criticism, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
+Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  The antecedent alignment remains context-dependent throughout, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>This instance presents a highly sophisticated structure where the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -5167,21 +5167,21 @@
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Based on the provided textual input, the system detects a classical syntactic ambiguity issue. The semantic mismatch forces the listener to abandon a purely literal interpretation, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Checking for implicit intent and metaphors. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, resulting in an accurate formulation of the expected key elements.</t>
+          <t>A deep semantic analysis of the scenario shows that the structural ambiguity must be resolved via hierarchical mapping.  This requires the model to activate shared background knowledge, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -5196,21 +5196,21 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
-          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
+          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The singular pronoun resolution depends heavily on the organizational hierarchy, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the interlocutors rely on a sustained satirical register.  The universal vs existential quantifier interaction triggers dual readings, allowing for a precise mapping of pragmatic intent.</t>
+          <t>This instance presents a highly sophisticated structure where the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -5225,13 +5225,13 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the model successfully identifies a clear instance of verbal irony. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
+          <t>In this specific scenario, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
+User wants to detect sarcasm. Identifying the rhetorical device used by the speaker. Coping humor found.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the interlocutors rely on a sustained satirical register.  The universal vs existential quantifier interaction triggers dual readings, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -5258,21 +5258,21 @@
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The inverse scope reading compresses the entity domain significantly, which requires deep contextual mapping to resolve.</t>
+          <t>Regarding the linguistic cues in this context, the text introduces a complex quantifier scope interaction. The semantic mismatch forces the listener to abandon a purely literal interpretation, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the interlocutors rely on a sustained satirical register.  This highlights an obvious pragmatic contradiction in the literal text, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -5287,21 +5287,21 @@
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the text introduces a complex quantifier scope interaction. The singular pronoun resolution depends heavily on the organizational hierarchy, ensuring the final output aligns with human common ground.</t>
+          <t>In this specific scenario, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -5320,13 +5320,13 @@
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, there is a prominent coreference resolution challenge. The literal wording directly contradicts the actual situational reality, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Regarding the linguistic cues in this context, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, which is critical for robust dialogue understanding.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -5349,13 +5349,13 @@
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the model successfully identifies a clear instance of verbal irony. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>According to the pragmatic features observed here, the model successfully identifies a clear instance of verbal irony. The literal wording directly contradicts the actual situational reality, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the structural ambiguity must be resolved via hierarchical mapping.  The negative situational reality deflates the surface-level politeness, which is critical for robust dialogue understanding.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -5378,21 +5378,21 @@
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, which requires deep contextual mapping to resolve.</t>
+          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The singular pronoun resolution depends heavily on the organizational hierarchy, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the interlocutors rely on a sustained satirical register.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
+          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -5411,21 +5411,21 @@
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the speaker exhibits implicit intent masked by a polite register. The singular pronoun resolution depends heavily on the organizational hierarchy, demonstrating advanced linguistic nuance decoding.</t>
+          <t>According to the pragmatic features observed here, there is a prominent coreference resolution challenge. The semantic mismatch forces the listener to abandon a purely literal interpretation, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the interlocutors rely on a sustained satirical register.  This requires the model to activate shared background knowledge, preventing a naive or literal failure mode.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -5440,13 +5440,13 @@
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
-          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
+          <t>According to the pragmatic features observed here, the speaker exhibits implicit intent masked by a polite register. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+Checking for implicit intent and metaphors. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the interlocutors rely on a sustained satirical register.  The antecedent alignment remains context-dependent throughout, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -5473,21 +5473,21 @@
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Analyzing the semantic structure of this prompt, the speaker exhibits implicit intent masked by a polite register. The literal wording directly contradicts the actual situational reality, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the interlocutors rely on a sustained satirical register.  This requires the model to activate shared background knowledge, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  The antecedent alignment remains context-dependent throughout, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -5502,21 +5502,21 @@
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the speaker exhibits implicit intent masked by a polite register. The literal wording directly contradicts the actual situational reality, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Regarding the linguistic cues in this context, the text introduces a complex quantifier scope interaction. The semantic mismatch forces the listener to abandon a purely literal interpretation, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
+          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -5540,12 +5540,12 @@
 User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
 End of analysis. Outputting final response.
 &lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  The universal vs existential quantifier interaction triggers dual readings, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>From a comprehensive pragmatic perspective, the structural ambiguity must be resolved via hierarchical mapping.  The antecedent alignment remains context-dependent throughout, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
-          <t>In this specific scenario, there is a prominent coreference resolution challenge. The singular pronoun resolution depends heavily on the organizational hierarchy, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Regarding the linguistic cues in this context, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -5569,12 +5569,12 @@
 Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
 End of analysis. Outputting final response.
 &lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the bound-variable pronoun requires meticulous reference pruning.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>A deep semantic analysis of the scenario shows that the bound-variable pronoun requires meticulous reference pruning.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -5593,21 +5593,21 @@
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The singular pronoun resolution depends heavily on the organizational hierarchy, ensuring the final output aligns with human common ground.</t>
+          <t>Regarding the linguistic cues in this context, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the structural ambiguity must be resolved via hierarchical mapping.  The universal vs existential quantifier interaction triggers dual readings, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the conceptual metaphor subverts the conventional meaning of the phrase.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the speaker exhibits implicit intent masked by a polite register. The singular pronoun resolution depends heavily on the organizational hierarchy, thus successfully extracting the true underlying sentiment.</t>
+          <t>Regarding the linguistic cues in this context, the system detects a classical syntactic ambiguity issue. The singular pronoun resolution depends heavily on the organizational hierarchy, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -5631,12 +5631,12 @@
 Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the bound-variable pronoun requires meticulous reference pruning.  The antecedent alignment remains context-dependent throughout, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>This instance presents a highly sophisticated structure where the speaker utilizes a tactical sarcastic feint to convey disappointment.  The universal vs existential quantifier interaction triggers dual readings, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -5655,21 +5655,21 @@
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, thus successfully extracting the true underlying sentiment.</t>
+          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -5684,13 +5684,13 @@
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
-          <t>In this specific scenario, there is a prominent coreference resolution challenge. The semantic mismatch forces the listener to abandon a purely literal interpretation, demonstrating advanced linguistic nuance decoding.</t>
+          <t>In this specific scenario, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Identifying the rhetorical device used by the speaker. Coping humor found.
+User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
+          <t>A deep semantic analysis of the scenario shows that the bound-variable pronoun requires meticulous reference pruning.  The antecedent alignment remains context-dependent throughout, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -5717,13 +5717,13 @@
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>In this specific scenario, there is a prominent coreference resolution challenge. The literal wording directly contradicts the actual situational reality, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
@@ -5731,7 +5731,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  The universal vs existential quantifier interaction triggers dual readings, preventing a naive or literal failure mode.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -5746,21 +5746,21 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Based on the provided textual input, the text introduces a complex quantifier scope interaction. The lexical choices function metaphorically to deliver passive criticism, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The universal vs existential quantifier interaction triggers dual readings, allowing for a precise mapping of pragmatic intent.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the interlocutors rely on a sustained satirical register.  The antecedent alignment remains context-dependent throughout, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -5779,13 +5779,13 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, demonstrating advanced linguistic nuance decoding.</t>
+          <t>According to the pragmatic features observed here, the system detects a classical syntactic ambiguity issue. The semantic mismatch forces the listener to abandon a purely literal interpretation, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+User wants to detect sarcasm. Identifying the rhetorical device used by the speaker. Coping humor found.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the structural ambiguity must be resolved via hierarchical mapping.  The universal vs existential quantifier interaction triggers dual readings, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>This instance presents a highly sophisticated structure where the speaker utilizes a tactical sarcastic feint to convey disappointment.  The universal vs existential quantifier interaction triggers dual readings, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -5808,21 +5808,21 @@
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the model successfully identifies a clear instance of verbal irony. The inverse scope reading compresses the entity domain significantly, thus successfully extracting the true underlying sentiment.</t>
+          <t>Based on the provided textual input, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>This instance presents a highly sophisticated structure where the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -5841,13 +5841,13 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the text introduces a complex quantifier scope interaction. The lexical choices function metaphorically to deliver passive criticism, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Regarding the linguistic cues in this context, there is a prominent coreference resolution challenge. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
+User wants to detect sarcasm. Identifying the rhetorical device used by the speaker. Coping humor found.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, preventing a naive or literal failure mode.</t>
+          <t>From a comprehensive pragmatic perspective, the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -5870,13 +5870,13 @@
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the model successfully identifies a clear instance of verbal irony. The singular pronoun resolution depends heavily on the organizational hierarchy, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Regarding the linguistic cues in this context, the system detects a classical syntactic ambiguity issue. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  The universal vs existential quantifier interaction triggers dual readings, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the model successfully identifies a clear instance of verbal irony. The literal wording directly contradicts the actual situational reality, ensuring the final output aligns with human common ground.</t>
+          <t>According to the pragmatic features observed here, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -5912,12 +5912,12 @@
 Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
 End of analysis. Outputting final response.
 &lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  This requires the model to activate shared background knowledge, preventing a naive or literal failure mode.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the structural ambiguity must be resolved via hierarchical mapping.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -5932,21 +5932,21 @@
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
-          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The inverse scope reading compresses the entity domain significantly, ensuring the final output aligns with human common ground.</t>
+          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The semantic mismatch forces the listener to abandon a purely literal interpretation, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, preventing a naive or literal failure mode.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -5965,21 +5965,21 @@
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, which requires deep contextual mapping to resolve.</t>
+          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The lexical choices function metaphorically to deliver passive criticism, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the structural ambiguity must be resolved via hierarchical mapping.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
+          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -5994,21 +5994,21 @@
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the speaker exhibits implicit intent masked by a polite register. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The semantic mismatch forces the listener to abandon a purely literal interpretation, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the structural ambiguity must be resolved via hierarchical mapping.  The negative situational reality deflates the surface-level politeness, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -6023,13 +6023,13 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the text introduces a complex quantifier scope interaction. The inverse scope reading compresses the entity domain significantly, ensuring the final output aligns with human common ground.</t>
+          <t>Analyzing the semantic structure of this prompt, the speaker exhibits implicit intent masked by a polite register. The singular pronoun resolution depends heavily on the organizational hierarchy, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the conceptual metaphor subverts the conventional meaning of the phrase.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
+          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  This requires the model to activate shared background knowledge, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -6052,13 +6052,13 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
-          <t>In this specific scenario, the text introduces a complex quantifier scope interaction. The lexical choices function metaphorically to deliver passive criticism, ensuring the final output aligns with human common ground.</t>
+          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The semantic mismatch forces the listener to abandon a purely literal interpretation, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, which is critical for robust dialogue understanding.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  The antecedent alignment remains context-dependent throughout, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -6085,21 +6085,21 @@
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
-          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>According to the pragmatic features observed here, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Checking for implicit intent and metaphors. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the conceptual metaphor subverts the conventional meaning of the phrase.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -6114,21 +6114,21 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
-          <t>In this specific scenario, the speaker exhibits implicit intent masked by a polite register. The lexical choices function metaphorically to deliver passive criticism, thus successfully extracting the true underlying sentiment.</t>
+          <t>According to the pragmatic features observed here, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The antecedent alignment remains context-dependent throughout, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>This instance presents a highly sophisticated structure where the bound-variable pronoun requires meticulous reference pruning.  The antecedent alignment remains context-dependent throughout, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -6147,21 +6147,21 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The semantic mismatch forces the listener to abandon a purely literal interpretation, ensuring the final output aligns with human common ground.</t>
+          <t>Based on the provided textual input, the text introduces a complex quantifier scope interaction. The semantic mismatch forces the listener to abandon a purely literal interpretation, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, preventing a naive or literal failure mode.</t>
+          <t>From a comprehensive pragmatic perspective, the conceptual metaphor subverts the conventional meaning of the phrase.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -6176,21 +6176,21 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the structural ambiguity must be resolved via hierarchical mapping.  The negative situational reality deflates the surface-level politeness, which is critical for robust dialogue understanding.</t>
+          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -6209,21 +6209,21 @@
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the speaker exhibits implicit intent masked by a polite register. The lexical choices function metaphorically to deliver passive criticism, which requires deep contextual mapping to resolve.</t>
+          <t>Regarding the linguistic cues in this context, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Checking for implicit intent and metaphors. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  The universal vs existential quantifier interaction triggers dual readings, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -6238,21 +6238,21 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, there is a prominent coreference resolution challenge. The singular pronoun resolution depends heavily on the organizational hierarchy, thus successfully extracting the true underlying sentiment.</t>
+          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The semantic mismatch forces the listener to abandon a purely literal interpretation, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the structural ambiguity must be resolved via hierarchical mapping.  The universal vs existential quantifier interaction triggers dual readings, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the conceptual metaphor subverts the conventional meaning of the phrase.  The antecedent alignment remains context-dependent throughout, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -6267,21 +6267,21 @@
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, which requires deep contextual mapping to resolve.</t>
+          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The singular pronoun resolution depends heavily on the organizational hierarchy, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the structural ambiguity must be resolved via hierarchical mapping.  This highlights an obvious pragmatic contradiction in the literal text, preventing a naive or literal failure mode.</t>
+          <t>This instance presents a highly sophisticated structure where the structural ambiguity must be resolved via hierarchical mapping.  The universal vs existential quantifier interaction triggers dual readings, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -6296,21 +6296,21 @@
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the model successfully identifies a clear instance of verbal irony. The semantic mismatch forces the listener to abandon a purely literal interpretation, demonstrating advanced linguistic nuance decoding.</t>
+          <t>In this specific scenario, there is a prominent coreference resolution challenge. The singular pronoun resolution depends heavily on the organizational hierarchy, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the interlocutors rely on a sustained satirical register.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
+          <t>From a comprehensive pragmatic perspective, the structural ambiguity must be resolved via hierarchical mapping.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -6329,13 +6329,13 @@
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
-          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The lexical choices function metaphorically to deliver passive criticism, ensuring the final output aligns with human common ground.</t>
+          <t>In this specific scenario, the speaker exhibits implicit intent masked by a polite register. The singular pronoun resolution depends heavily on the organizational hierarchy, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Identifying the rhetorical device used by the speaker. Coping humor found.
+User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  The antecedent alignment remains context-dependent throughout, which is critical for robust dialogue understanding.</t>
+          <t>From a comprehensive pragmatic perspective, the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -6358,21 +6358,21 @@
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the text introduces a complex quantifier scope interaction. The semantic mismatch forces the listener to abandon a purely literal interpretation, ensuring the final output aligns with human common ground.</t>
+          <t>Analyzing the semantic structure of this prompt, the model successfully identifies a clear instance of verbal irony. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
+          <t>A deep semantic analysis of the scenario shows that the structural ambiguity must be resolved via hierarchical mapping.  The antecedent alignment remains context-dependent throughout, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -6391,13 +6391,13 @@
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, thus successfully extracting the true underlying sentiment.</t>
+          <t>According to the pragmatic features observed here, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the interlocutors rely on a sustained satirical register.  The universal vs existential quantifier interaction triggers dual readings, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the text introduces a complex quantifier scope interaction. The semantic mismatch forces the listener to abandon a purely literal interpretation, thus successfully extracting the true underlying sentiment.</t>
+          <t>According to the pragmatic features observed here, there is a prominent coreference resolution challenge. The lexical choices function metaphorically to deliver passive criticism, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -6429,12 +6429,12 @@
 User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
 End of analysis. Outputting final response.
 &lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
+          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  The universal vs existential quantifier interaction triggers dual readings, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -6453,21 +6453,21 @@
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, there is a prominent coreference resolution challenge. The literal wording directly contradicts the actual situational reality, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Based on the provided textual input, the model successfully identifies a clear instance of verbal irony. The semantic mismatch forces the listener to abandon a purely literal interpretation, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Linguistic evaluation of this dialogue indicates that the bound-variable pronoun requires meticulous reference pruning.  The antecedent alignment remains context-dependent throughout, resulting in an accurate formulation of the expected key elements.</t>
+          <t>A deep semantic analysis of the scenario shows that the bound-variable pronoun requires meticulous reference pruning.  This highlights an obvious pragmatic contradiction in the literal text, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -6482,21 +6482,21 @@
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The singular pronoun resolution depends heavily on the organizational hierarchy, which requires deep contextual mapping to resolve.</t>
+          <t>In this specific scenario, the text introduces a complex quantifier scope interaction. The lexical choices function metaphorically to deliver passive criticism, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  The antecedent alignment remains context-dependent throughout, resulting in an accurate formulation of the expected key elements.</t>
+          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -6511,21 +6511,21 @@
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
-          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The inverse scope reading compresses the entity domain significantly, demonstrating advanced linguistic nuance decoding.</t>
+          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The lexical choices function metaphorically to deliver passive criticism, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Checking for implicit intent and metaphors. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The universal vs existential quantifier interaction triggers dual readings, allowing for a precise mapping of pragmatic intent.</t>
+          <t>From a comprehensive pragmatic perspective, the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -6540,21 +6540,21 @@
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, which requires deep contextual mapping to resolve.</t>
+          <t>Based on the provided textual input, the model successfully identifies a clear instance of verbal irony. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>This instance presents a highly sophisticated structure where the interlocutors rely on a sustained satirical register.  The antecedent alignment remains context-dependent throughout, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
@@ -6573,21 +6573,21 @@
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
+          <t>Regarding the linguistic cues in this context, the text introduces a complex quantifier scope interaction. The singular pronoun resolution depends heavily on the organizational hierarchy, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  The universal vs existential quantifier interaction triggers dual readings, allowing for a precise mapping of pragmatic intent.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -6602,21 +6602,21 @@
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, the system detects a classical syntactic ambiguity issue. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
+          <t>Analyzing the semantic structure of this prompt, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
+          <t>This instance presents a highly sophisticated structure where the structural ambiguity must be resolved via hierarchical mapping.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -6635,21 +6635,21 @@
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
-          <t>In this specific scenario, the model successfully identifies a clear instance of verbal irony. The inverse scope reading compresses the entity domain significantly, demonstrating advanced linguistic nuance decoding.</t>
+          <t>In this specific scenario, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Mapping the pronouns to their respective antecedents based on context.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the interlocutors rely on a sustained satirical register.  The universal vs existential quantifier interaction triggers dual readings, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6664,7 @@
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, which requires deep contextual mapping to resolve.</t>
+          <t>Analyzing the semantic structure of this prompt, there is a prominent coreference resolution challenge. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -6673,12 +6673,12 @@
 Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
 End of analysis. Outputting final response.
 &lt;/think&gt;
-Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
+Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  The universal vs existential quantifier interaction triggers dual readings, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the structural ambiguity must be resolved via hierarchical mapping.  This highlights an obvious pragmatic contradiction in the literal text, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -6697,21 +6697,21 @@
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The singular pronoun resolution depends heavily on the organizational hierarchy, ensuring the final output aligns with human common ground.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Resolution: This presents a clear scope ambiguity problem. The surface reading suggests multiple tracks, while the inverse reading compresses the domain.</t>
+Analyzing coreference resolution in this text. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>This instance presents a highly sophisticated structure where the speaker utilizes a tactical sarcastic feint to convey disappointment.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
+          <t>A deep semantic analysis of the scenario shows that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The antecedent alignment remains context-dependent throughout, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -6726,21 +6726,21 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the system detects a classical syntactic ambiguity issue. The semantic mismatch forces the listener to abandon a purely literal interpretation, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The semantic mismatch forces the listener to abandon a purely literal interpretation, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+User wants to detect sarcasm. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, which is critical for robust dialogue understanding.</t>
+          <t>Linguistic evaluation of this dialogue indicates that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -6755,13 +6755,13 @@
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the speaker exhibits implicit intent masked by a polite register. The literal wording directly contradicts the actual situational reality, thus successfully extracting the true underlying sentiment.</t>
+          <t>According to the pragmatic features observed here, there is a prominent coreference resolution challenge. The inverse scope reading compresses the entity domain significantly, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+Checking for implicit intent and metaphors. Mapping the pronouns to their respective antecedents based on context.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, resulting in an accurate formulation of the expected key elements.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  This requires the model to activate shared background knowledge, allowing for a precise mapping of pragmatic intent.</t>
         </is>
       </c>
     </row>
@@ -6784,13 +6784,13 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
-          <t>According to the pragmatic features observed here, the text introduces a complex quantifier scope interaction. The lexical choices function metaphorically to deliver passive criticism, highlighting the model's capability in pragmatic comprehension.</t>
+          <t>Regarding the linguistic cues in this context, the text introduces a complex quantifier scope interaction. The literal wording directly contradicts the actual situational reality, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Mapping the pronouns to their respective antecedents based on context.
+Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the conceptual metaphor subverts the conventional meaning of the phrase.  The universal vs existential quantifier interaction triggers dual readings, allowing for a precise mapping of pragmatic intent.</t>
+          <t>Evaluating the lexical density of the exchange reveals that the speaker utilizes a tactical sarcastic feint to convey disappointment.  The negative situational reality deflates the surface-level politeness, showcasing superior performance in high-level NLP benchmarks.</t>
         </is>
       </c>
     </row>
@@ -6817,13 +6817,13 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Regarding the linguistic cues in this context, the system detects a classical syntactic ambiguity issue. The lexical choices function metaphorically to deliver passive criticism, which requires deep contextual mapping to resolve.</t>
+          <t>In this specific scenario, the system detects a classical syntactic ambiguity issue. The singular pronoun resolution depends heavily on the organizational hierarchy, highlighting the model's capability in pragmatic comprehension.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Identifying the rhetorical device used by the speaker. Coping humor found.
+User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
 End of analysis. Outputting final response.
 &lt;/think&gt;
 Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Evaluating the lexical density of the exchange reveals that the bound-variable pronoun requires meticulous reference pruning.  The negative situational reality deflates the surface-level politeness, resulting in an accurate formulation of the expected key elements.</t>
+          <t>From a comprehensive pragmatic perspective, the bound-variable pronoun requires meticulous reference pruning.  The antecedent alignment remains context-dependent throughout, preventing a naive or literal failure mode.</t>
         </is>
       </c>
     </row>
@@ -6846,21 +6846,21 @@
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Based on the provided textual input, there is a prominent coreference resolution challenge. The singular pronoun resolution depends heavily on the organizational hierarchy, demonstrating advanced linguistic nuance decoding.</t>
+          <t>In this specific scenario, the speaker exhibits implicit intent masked by a polite register. The semantic mismatch forces the listener to abandon a purely literal interpretation, which requires deep contextual mapping to resolve.</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Evaluating structural ambiguity and quantifiers. Situation is negative but words are positive. Mismatch detected. Conclusion: Verbal irony.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
+Evaluating structural ambiguity and quantifiers. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Coreference Alignment: The pronoun maps accurately to the designated subject. The linguistic nuances are fully captured without breaking structural constraints.</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>A deep semantic analysis of the scenario shows that the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>This instance presents a highly sophisticated structure where the conceptual metaphor subverts the conventional meaning of the phrase.  This highlights an obvious pragmatic contradiction in the literal text, which is critical for robust dialogue understanding.</t>
         </is>
       </c>
     </row>
@@ -6879,21 +6879,21 @@
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
-          <t>In this specific scenario, the text introduces a complex quantifier scope interaction. The semantic mismatch forces the listener to abandon a purely literal interpretation, which requires deep contextual mapping to resolve.</t>
+          <t>Based on the provided textual input, the system detects a classical syntactic ambiguity issue. The inverse scope reading compresses the entity domain significantly, demonstrating advanced linguistic nuance decoding.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
           <t>&lt;think&gt;
-Analyzing coreference resolution in this text. Identifying the rhetorical device used by the speaker. Coping humor found.
-End of analysis. Outputting final response.
-&lt;/think&gt;
-Evaluation: The speaker uses a sarcastic feint. The response successfully decodes the passive criticism embedded within the workplace dialogue.</t>
+User wants to detect sarcasm. Checking surface scope vs inverse scope entities. Minimum entities needed calculation.
+End of analysis. Outputting final response.
+&lt;/think&gt;
+Analysis: The model identifies the pragmatic mismatch. The statement should not be taken literally as the situational context forces an inversion of meaning.</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>From a comprehensive pragmatic perspective, the speaker utilizes a tactical sarcastic feint to convey disappointment.  The universal vs existential quantifier interaction triggers dual readings, showcasing superior performance in high-level NLP benchmarks.</t>
+          <t>This instance presents a highly sophisticated structure where the bound-variable pronoun requires meticulous reference pruning.  This highlights an obvious pragmatic contradiction in the literal text, resulting in an accurate formulation of the expected key elements.</t>
         </is>
       </c>
     </row>
